--- a/healthcare_forms/005_healthcare_professional_time_tracking--healthcare_forms.xlsx
+++ b/healthcare_forms/005_healthcare_professional_time_tracking--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>role_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Role 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>unit_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>shift</t>
+          <t>shift_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Shift 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
